--- a/Data/elec_to_gas_coefficients.xlsx
+++ b/Data/elec_to_gas_coefficients.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{B317BB48-7D99-4E7D-BF8C-3D71FB77F8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4893038-E4EE-4806-A06C-C8B9100D5EC7}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{B317BB48-7D99-4E7D-BF8C-3D71FB77F8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8014DCCF-34C3-4883-8B78-1CDEB3110508}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{5DB4381E-6AD4-4247-9853-321D5AD15FA0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="3" xr2:uid="{5DB4381E-6AD4-4247-9853-321D5AD15FA0}"/>
   </bookViews>
   <sheets>
     <sheet name="coefficients" sheetId="1" r:id="rId1"/>
     <sheet name="hot water" sheetId="2" r:id="rId2"/>
     <sheet name="hot water (heatpump numbers)" sheetId="6" r:id="rId3"/>
-    <sheet name="cooking" sheetId="4" r:id="rId4"/>
-    <sheet name="cooking - frontier energy" sheetId="7" r:id="rId5"/>
-    <sheet name="space conditioning" sheetId="5" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId7"/>
+    <sheet name="cooking - frontier energy" sheetId="7" r:id="rId4"/>
+    <sheet name="space conditioning" sheetId="5" r:id="rId5"/>
+    <sheet name="cooking" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t>end_use</t>
   </si>
@@ -91,21 +90,6 @@
   </si>
   <si>
     <t>gas_consumption_MJ</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>Stock</t>
-  </si>
-  <si>
-    <t>PJ/app</t>
-  </si>
-  <si>
-    <t>KWh /app</t>
-  </si>
-  <si>
-    <t>(electric water heaters)</t>
   </si>
   <si>
     <t>gas_consumption_KWH</t>
@@ -268,7 +252,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +266,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -291,7 +282,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -299,43 +290,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -782,21 +750,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6649CEED-F841-42C6-A955-9ECD33AE160B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
-    <col min="2" max="2" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -805,7 +773,7 @@
         <v>0.42805755395683454</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -814,7 +782,7 @@
         <v>0.819210941407302</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -822,7 +790,7 @@
         <v>0.2</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -833,34 +801,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4411AA97-226F-40A1-B669-1B7E7324C4E9}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="105.125" customWidth="1"/>
-    <col min="2" max="2" width="21.875" customWidth="1"/>
-    <col min="3" max="3" width="22.625" customWidth="1"/>
-    <col min="4" max="4" width="19.125" customWidth="1"/>
+    <col min="1" max="1" width="105.08203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="22.58203125" customWidth="1"/>
+    <col min="4" max="4" width="19.08203125" customWidth="1"/>
     <col min="10" max="10" width="68.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="285.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="285.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -869,13 +837,13 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -894,7 +862,7 @@
         <v>0.819210941407302</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1771</v>
       </c>
@@ -918,61 +886,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4FCBE2-01F2-40B4-9C2B-DF4F15FCD3F9}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.58203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="4">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2">
         <v>4882</v>
       </c>
       <c r="C3">
@@ -983,7 +951,7 @@
         <v>1428.1960000000001</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>559</v>
@@ -997,11 +965,11 @@
         <v>0.39140286067178448</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="4">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2">
         <v>7134</v>
       </c>
       <c r="C4">
@@ -1012,7 +980,7 @@
         <v>2054.2520000000004</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>714</v>
@@ -1026,11 +994,11 @@
         <v>0.34757176821538927</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="4">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2">
         <v>6562</v>
       </c>
       <c r="C5">
@@ -1041,7 +1009,7 @@
         <v>1895.2360000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F5">
         <v>673</v>
@@ -1055,11 +1023,11 @@
         <v>0.35510089508641668</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="4">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2">
         <v>5810</v>
       </c>
       <c r="C6">
@@ -1070,7 +1038,7 @@
         <v>1686.18</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F6">
         <v>620</v>
@@ -1084,11 +1052,11 @@
         <v>0.36769502662823661</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="4">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2">
         <v>6253</v>
       </c>
       <c r="C7">
@@ -1099,7 +1067,7 @@
         <v>1809.3340000000001</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F7">
         <v>652</v>
@@ -1113,11 +1081,11 @@
         <v>0.36035358866853767</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="4">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2">
         <v>4203</v>
       </c>
       <c r="C8">
@@ -1128,7 +1096,7 @@
         <v>1239.4340000000002</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>508</v>
@@ -1142,11 +1110,11 @@
         <v>0.40986450266815327</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2">
         <v>6170</v>
       </c>
       <c r="C9">
@@ -1157,7 +1125,7 @@
         <v>1786.2600000000002</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F9">
         <v>648</v>
@@ -1171,11 +1139,11 @@
         <v>0.3627691377515031</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="4">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2">
         <v>5046</v>
       </c>
       <c r="C10">
@@ -1186,7 +1154,7 @@
         <v>1473.7880000000002</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F10">
         <v>568</v>
@@ -1200,11 +1168,11 @@
         <v>0.38540142815655976</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2">
         <v>6747</v>
       </c>
       <c r="C11">
@@ -1215,7 +1183,7 @@
         <v>1946.6660000000002</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F11">
         <v>691</v>
@@ -1229,11 +1197,11 @@
         <v>0.35496587498831333</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="4">
+        <v>27</v>
+      </c>
+      <c r="B12" s="2">
         <v>5800</v>
       </c>
       <c r="C12">
@@ -1244,7 +1212,7 @@
         <v>1683.4</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>624</v>
@@ -1258,11 +1226,11 @@
         <v>0.37067838897469407</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="4">
+        <v>28</v>
+      </c>
+      <c r="B13" s="2">
         <v>4925</v>
       </c>
       <c r="C13">
@@ -1273,7 +1241,7 @@
         <v>1440.15</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13">
         <v>564</v>
@@ -1287,11 +1255,11 @@
         <v>0.3916258723049682</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="4">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2">
         <v>4656</v>
       </c>
       <c r="C14">
@@ -1302,9 +1270,9 @@
         <v>1365.3680000000002</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="4">
+        <v>33</v>
+      </c>
+      <c r="F14" s="2">
         <v>544</v>
       </c>
       <c r="G14">
@@ -1315,13 +1283,13 @@
         <f t="shared" si="2"/>
         <v>0.3984273836797112</v>
       </c>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="4">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2">
         <v>4898</v>
       </c>
       <c r="C15">
@@ -1332,9 +1300,9 @@
         <v>1432.6440000000002</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="4">
+        <v>29</v>
+      </c>
+      <c r="F15" s="2">
         <v>559</v>
       </c>
       <c r="G15">
@@ -1345,13 +1313,13 @@
         <f t="shared" si="2"/>
         <v>0.39018765303871716</v>
       </c>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="4">
+        <v>34</v>
+      </c>
+      <c r="B16" s="2">
         <v>6096</v>
       </c>
       <c r="C16">
@@ -1362,9 +1330,9 @@
         <v>1765.6880000000001</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="4">
+        <v>34</v>
+      </c>
+      <c r="F16" s="2">
         <v>642</v>
       </c>
       <c r="G16">
@@ -1375,13 +1343,13 @@
         <f t="shared" si="2"/>
         <v>0.36359764579019621</v>
       </c>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="4">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2">
         <v>6185</v>
       </c>
       <c r="C17">
@@ -1392,9 +1360,9 @@
         <v>1790.43</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="4">
+        <v>35</v>
+      </c>
+      <c r="F17" s="2">
         <v>651</v>
       </c>
       <c r="G17">
@@ -1405,13 +1373,13 @@
         <f t="shared" si="2"/>
         <v>0.36359980563328359</v>
       </c>
-      <c r="J17" s="4"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="4">
+        <v>30</v>
+      </c>
+      <c r="B18" s="2">
         <v>6263</v>
       </c>
       <c r="C18">
@@ -1422,9 +1390,9 @@
         <v>1812.1140000000003</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" s="4">
+        <v>30</v>
+      </c>
+      <c r="F18" s="2">
         <v>656</v>
       </c>
       <c r="G18">
@@ -1435,56 +1403,56 @@
         <f t="shared" si="2"/>
         <v>0.36200812973135238</v>
       </c>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="J19" s="4"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H20" s="4"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H21" s="4"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H22" s="4"/>
-      <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H23" s="4"/>
-      <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H24" s="4"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H25" s="4"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H27" s="4"/>
-      <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H29" s="4"/>
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="H30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H30" s="2"/>
+      <c r="J30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1492,124 +1460,71 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D7E954-291B-4927-A0A3-E8DD7A018040}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72B2A2F-97F0-4C52-8ABB-CC8C8841DC51}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.5" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0.755</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.31900000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2000</v>
-      </c>
-      <c r="B4">
-        <v>1000</v>
-      </c>
-      <c r="C4">
-        <f>B4/A4</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72B2A2F-97F0-4C52-8ABB-CC8C8841DC51}">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="21.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="27.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" t="s">
         <v>52</v>
-      </c>
-      <c r="E1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="5">
-        <v>0.85199999999999998</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.86099999999999999</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0.83</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0.755</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0.79300000000000004</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0.31900000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>57</v>
       </c>
       <c r="B3">
         <v>0.56299999999999994</v>
@@ -1630,9 +1545,9 @@
         <v>5.43</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B4">
         <v>0.23799999999999999</v>
@@ -1653,9 +1568,9 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B5">
         <v>0.16900000000000001</v>
@@ -1676,9 +1591,9 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B6">
         <f>SUM(B3:B5)</f>
@@ -1709,9 +1624,9 @@
         <v>2.3908</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B7">
         <f>B6/H6</f>
@@ -1734,9 +1649,9 @@
         <v>0.4550777982265351</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B11">
         <f xml:space="preserve"> AVERAGE(B7:F7)</f>
@@ -1748,10 +1663,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C47217-C2F6-41E0-A11F-B459D1761CCF}">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
@@ -1760,43 +1675,43 @@
     <col min="5" max="5" width="11.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="4">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
         <v>30196</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="2">
         <f>B2*0.278</f>
         <v>8394.4880000000012</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>25</v>
+      <c r="D2" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E2">
         <v>1295</v>
@@ -1806,19 +1721,19 @@
         <v>0.15426789579066644</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="4">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2">
         <v>59041</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="2">
         <f t="shared" ref="C3:C16" si="0">B3*0.278</f>
         <v>16413.398000000001</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>26</v>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="E3">
         <v>2121</v>
@@ -1828,19 +1743,19 @@
         <v>0.12922369883433033</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="4">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2">
         <v>60039</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="2">
         <f t="shared" si="0"/>
         <v>16690.842000000001</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>27</v>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="E4">
         <v>2177</v>
@@ -1850,19 +1765,19 @@
         <v>0.1304308075050977</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="4">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2">
         <v>35312</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>9816.7360000000008</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>28</v>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="E5">
         <v>1447</v>
@@ -1872,22 +1787,22 @@
         <v>0.14740133584115941</v>
       </c>
       <c r="M5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="4">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2">
         <v>70560</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>19615.68</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E6">
         <v>2442</v>
@@ -1901,19 +1816,19 @@
         <v>0.22564102564102564</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="4">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2">
         <v>55671</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>15476.538000000002</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>37</v>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E7">
         <v>2077</v>
@@ -1923,19 +1838,19 @@
         <v>0.13420314026302263</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="4">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2">
         <v>32141</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>8935.1980000000003</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>30</v>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E8">
         <v>1380</v>
@@ -1945,19 +1860,19 @@
         <v>0.15444537434984651</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="4">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2">
         <v>69478</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>19314.884000000002</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>31</v>
+      <c r="D9" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E9">
         <v>2379</v>
@@ -1967,19 +1882,19 @@
         <v>0.12316926159121638</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="4">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
         <v>46753</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>12997.334000000001</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>32</v>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E10">
         <v>1758</v>
@@ -1989,19 +1904,19 @@
         <v>0.13525850762933384</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="4">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2">
         <v>32241</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>8962.9980000000014</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>33</v>
+      <c r="D11" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="E11">
         <v>1404</v>
@@ -2011,22 +1926,22 @@
         <v>0.15664401576347556</v>
       </c>
       <c r="M11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="4">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2">
         <v>12221</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="2">
         <f t="shared" si="0"/>
         <v>3397.4380000000001</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>38</v>
+      <c r="D12" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E12">
         <v>824</v>
@@ -2036,19 +1951,19 @@
         <v>0.24253569895903912</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="4">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
         <v>25120</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="2">
         <f t="shared" si="0"/>
         <v>6983.3600000000006</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>34</v>
+      <c r="D13" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="E13">
         <v>1171</v>
@@ -2058,19 +1973,19 @@
         <v>0.16768432387847682</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="4">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2">
         <v>45998</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="2">
         <f t="shared" si="0"/>
         <v>12787.444000000001</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>39</v>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E14">
         <v>1781</v>
@@ -2080,19 +1995,19 @@
         <v>0.13927724727474855</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="4">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2">
         <v>69115</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="2">
         <f t="shared" si="0"/>
         <v>19213.97</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>40</v>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E15">
         <v>2351</v>
@@ -2102,19 +2017,19 @@
         <v>0.12235888783005282</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="4">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2">
         <v>48526</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="2">
         <f t="shared" si="0"/>
         <v>13490.228000000001</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>35</v>
+      <c r="D16" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="E16">
         <v>1848</v>
@@ -2124,59 +2039,66 @@
         <v>0.13698804794107258</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C17" s="4"/>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J1" r:id="rId1" xr:uid="{015E93A5-D0FC-449A-BCCF-16B13D122E23}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3431E048-5131-4158-B890-BA5FE2DB0FE4}">
-  <dimension ref="B1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D7E954-291B-4927-A0A3-E8DD7A018040}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="27.25" customWidth="1"/>
+    <col min="1" max="1" width="19.5" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B2">
-        <v>2020</v>
-      </c>
-      <c r="C2" s="2">
-        <v>11.952774397080001</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1451196</v>
-      </c>
-      <c r="E2">
-        <f>C2/D2</f>
-        <v>8.2364989960556679E-6</v>
-      </c>
-      <c r="F2">
-        <f>E2*277800000</f>
-        <v>2288.0994211042644</v>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2000</v>
+      </c>
+      <c r="B4">
+        <v>1000</v>
+      </c>
+      <c r="C4">
+        <f>B4/A4</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="8:8" x14ac:dyDescent="0.3">
+      <c r="H25" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{3010381D-42BE-49B6-973A-DD675CED4482}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>